--- a/docs/Extras/SD2_S26/Bill-of-Materials-and-Budget/QORVO_RADIO2.xlsx
+++ b/docs/Extras/SD2_S26/Bill-of-Materials-and-Budget/QORVO_RADIO2.xlsx
@@ -29,7 +29,11 @@
 ID#AAAB3X6bO8o
 Emily Barron Aguilera    (2026-04-17 16:18:16)
 @lmatth23@charlotte.edu Your purchase is ready for pickup at the ISL office in the Cameron building, room 185. Please stop by during our office hours, which you can find on Canvas
-_Assigned to lmatth23@charlotte.edu_</t>
+_Assigned to lmatth23@charlotte.edu_
+------
+ID#AAAB3x4qbEE
+Amanda Keys    (2026-04-21 19:35:21)
+@lmatth23@charlotte.edu This order is still here. Check Canvas for office hours. Your mentor said the order is needed asap. You can send a team member directly to my office outside of office hours if needed.</t>
       </text>
     </comment>
     <comment authorId="0" ref="J24">
@@ -200,7 +204,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjT1Mi8JSRtJh4eVSFMDRWPBaonMA=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhXkLfkgDgS5mTZM9EBvhS+OzyfYg=="/>
     </ext>
   </extLst>
 </comments>
